--- a/scripts/data/50m_Masculino_Absoluto_Mariposa.xlsx
+++ b/scripts/data/50m_Masculino_Absoluto_Mariposa.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O83"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -675,22 +675,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C7" t="str">
-        <v>ALVARO TERUEL BELLOCH</v>
+        <v>ALEJANDRO FABIA NOGUERA</v>
       </c>
       <c r="D7">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="E7" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F7" t="str">
-        <v>00:00:28.46</v>
+        <v>00:00:28.29</v>
       </c>
       <c r="G7">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="H7" s="1">
-        <v>46045.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I7" t="str">
         <v>Deportista</v>
@@ -702,10 +702,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L7" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M7" t="str">
-        <v>Elche</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N7" t="str">
         <v>No</v>
@@ -719,22 +719,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C8" t="str">
-        <v>JAUME MORENO ROMERO</v>
+        <v>ALVARO TERUEL BELLOCH</v>
       </c>
       <c r="D8">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="E8" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F8" t="str">
-        <v>00:00:28.49</v>
+        <v>00:00:28.46</v>
       </c>
       <c r="G8">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H8" s="1">
-        <v>46074.99949074074</v>
+        <v>46045.99949074074</v>
       </c>
       <c r="I8" t="str">
         <v>Deportista</v>
@@ -746,7 +746,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L8" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M8" t="str">
         <v>Elche</v>
@@ -763,22 +763,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C9" t="str">
-        <v>DAVID HERREROS COLL</v>
+        <v>JAUME MORENO ROMERO</v>
       </c>
       <c r="D9">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="E9" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F9" t="str">
-        <v>00:00:28.56</v>
+        <v>00:00:28.49</v>
       </c>
       <c r="G9">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H9" s="1">
-        <v>46171.99949074074</v>
+        <v>46074.99949074074</v>
       </c>
       <c r="I9" t="str">
         <v>Deportista</v>
@@ -787,13 +787,13 @@
         <v>50m</v>
       </c>
       <c r="K9" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L9" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
       </c>
       <c r="M9" t="str">
-        <v>Vila-Real</v>
+        <v>Elche</v>
       </c>
       <c r="N9" t="str">
         <v>No</v>
@@ -807,22 +807,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C10" t="str">
-        <v>DANIEL FERNANDEZ CARO</v>
+        <v>DAVID HERREROS COLL</v>
       </c>
       <c r="D10">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="E10" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F10" t="str">
-        <v>00:00:28.59</v>
+        <v>00:00:28.56</v>
       </c>
       <c r="G10">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H10" s="1">
-        <v>45815.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I10" t="str">
         <v>Deportista</v>
@@ -831,13 +831,13 @@
         <v>50m</v>
       </c>
       <c r="K10" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L10" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M10" t="str">
-        <v>Castellón</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N10" t="str">
         <v>No</v>
@@ -851,22 +851,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C11" t="str">
-        <v>ALEJANDRO FABIA NOGUERA</v>
+        <v>DANIEL FERNANDEZ CARO</v>
       </c>
       <c r="D11">
-        <v>2012</v>
+        <v>2005</v>
       </c>
       <c r="E11" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F11" t="str">
-        <v>00:00:28.69</v>
+        <v>00:00:28.59</v>
       </c>
       <c r="G11">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="H11" s="1">
-        <v>46171.99949074074</v>
+        <v>45815.99949074074</v>
       </c>
       <c r="I11" t="str">
         <v>Deportista</v>
@@ -875,13 +875,13 @@
         <v>50m</v>
       </c>
       <c r="K11" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L11" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M11" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N11" t="str">
         <v>No</v>
@@ -1775,22 +1775,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C32" t="str">
-        <v>MARTIN FABIA NOGUERA</v>
+        <v>MARCOS PEDRERO MARTINEZ</v>
       </c>
       <c r="D32">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="E32" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F32" t="str">
-        <v>00:00:34.16</v>
+        <v>00:00:34.08</v>
       </c>
       <c r="G32">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H32" s="1">
-        <v>44709.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I32" t="str">
         <v>Deportista</v>
@@ -1799,13 +1799,13 @@
         <v>50m</v>
       </c>
       <c r="K32" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L32" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M32" t="str">
-        <v>Sedavi</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N32" t="str">
         <v>No</v>
@@ -1819,19 +1819,19 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C33" t="str">
-        <v>VICTOR ROSELLO VALERA</v>
+        <v>MARTIN FABIA NOGUERA</v>
       </c>
       <c r="D33">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="E33" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F33" t="str">
-        <v>00:00:34.53</v>
+        <v>00:00:34.16</v>
       </c>
       <c r="G33">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="H33" s="1">
         <v>44709.99949074074</v>
@@ -1863,7 +1863,7 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C34" t="str">
-        <v>HECTOR CARRASCO BLAZQUEZ</v>
+        <v>FELIPE SEBASTIAN HERMIDA BATTISTON</v>
       </c>
       <c r="D34">
         <v>2012</v>
@@ -1872,13 +1872,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F34" t="str">
-        <v>00:00:34.53</v>
+        <v>00:00:34.34</v>
       </c>
       <c r="G34">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="H34" s="1">
-        <v>46082.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I34" t="str">
         <v>Deportista</v>
@@ -1890,13 +1890,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L34" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M34" t="str">
-        <v>CASTELLÓN</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N34" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="35">
@@ -1907,22 +1907,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C35" t="str">
-        <v>CESAR ARROYO PEREZ</v>
+        <v>VICTOR ROSELLO VALERA</v>
       </c>
       <c r="D35">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="E35" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F35" t="str">
-        <v>00:00:34.57</v>
+        <v>00:00:34.53</v>
       </c>
       <c r="G35">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H35" s="1">
-        <v>45837.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I35" t="str">
         <v>Deportista</v>
@@ -1931,13 +1931,13 @@
         <v>50m</v>
       </c>
       <c r="K35" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L35" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M35" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N35" t="str">
         <v>No</v>
@@ -1951,22 +1951,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C36" t="str">
-        <v>DAVID ESCOBEDO IRUETA</v>
+        <v>HECTOR CARRASCO BLAZQUEZ</v>
       </c>
       <c r="D36">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="E36" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F36" t="str">
-        <v>00:00:34.60</v>
+        <v>00:00:34.53</v>
       </c>
       <c r="G36">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H36" s="1">
-        <v>44359.99949074074</v>
+        <v>46082.99949074074</v>
       </c>
       <c r="I36" t="str">
         <v>Deportista</v>
@@ -1978,13 +1978,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L36" t="str">
-        <v>IX Trofeo Real Club Natación Delfín</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M36" t="str">
-        <v>Sedavi</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N36" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="37">
@@ -1995,22 +1995,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C37" t="str">
-        <v>DANIEL DIAZ GONZALEZ</v>
+        <v>CESAR ARROYO PEREZ</v>
       </c>
       <c r="D37">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="E37" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F37" t="str">
-        <v>00:00:36.08</v>
+        <v>00:00:34.57</v>
       </c>
       <c r="G37">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="H37" s="1">
-        <v>46171.99949074074</v>
+        <v>45837.99949074074</v>
       </c>
       <c r="I37" t="str">
         <v>Deportista</v>
@@ -2019,13 +2019,13 @@
         <v>50m</v>
       </c>
       <c r="K37" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L37" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO 2025</v>
       </c>
       <c r="M37" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N37" t="str">
         <v>No</v>
@@ -2039,22 +2039,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C38" t="str">
-        <v>SIMON MORENO RODRIGUEZ</v>
+        <v>DAVID ESCOBEDO IRUETA</v>
       </c>
       <c r="D38">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="E38" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F38" t="str">
-        <v>00:00:36.50</v>
+        <v>00:00:34.60</v>
       </c>
       <c r="G38">
-        <v>227</v>
+        <v>267</v>
       </c>
       <c r="H38" s="1">
-        <v>45815.99949074074</v>
+        <v>44359.99949074074</v>
       </c>
       <c r="I38" t="str">
         <v>Deportista</v>
@@ -2066,13 +2066,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L38" t="str">
-        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>IX Trofeo Real Club Natación Delfín</v>
       </c>
       <c r="M38" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N38" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="39">
@@ -2083,22 +2083,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C39" t="str">
-        <v>FEDERICO MANUEL HERMIDA BATTISTON</v>
+        <v>DANIEL DIAZ GONZALEZ</v>
       </c>
       <c r="D39">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E39" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F39" t="str">
-        <v>00:00:39.00</v>
+        <v>00:00:36.08</v>
       </c>
       <c r="G39">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="H39" s="1">
-        <v>45682.99949074074</v>
+        <v>46171.99949074074</v>
       </c>
       <c r="I39" t="str">
         <v>Deportista</v>
@@ -2107,16 +2107,16 @@
         <v>50m</v>
       </c>
       <c r="K39" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L39" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M39" t="str">
-        <v>Elche</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N39" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="40">
@@ -2127,22 +2127,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C40" t="str">
-        <v>ALEXIS GARCIA VALERO</v>
+        <v>SIMON MORENO RODRIGUEZ</v>
       </c>
       <c r="D40">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="E40" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F40" t="str">
-        <v>00:00:39.46</v>
+        <v>00:00:36.50</v>
       </c>
       <c r="G40">
-        <v>180</v>
+        <v>227</v>
       </c>
       <c r="H40" s="1">
-        <v>45683.99949074074</v>
+        <v>45815.99949074074</v>
       </c>
       <c r="I40" t="str">
         <v>Deportista</v>
@@ -2154,13 +2154,13 @@
         <v>Electrónico</v>
       </c>
       <c r="L40" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>XIII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M40" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N40" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="41">
@@ -2171,7 +2171,7 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C41" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>FEDERICO MANUEL HERMIDA BATTISTON</v>
       </c>
       <c r="D41">
         <v>2010</v>
@@ -2180,13 +2180,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F41" t="str">
-        <v>00:00:43.21</v>
+        <v>00:00:39.00</v>
       </c>
       <c r="G41">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="H41" s="1">
-        <v>45255.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I41" t="str">
         <v>Deportista</v>
@@ -2198,10 +2198,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L41" t="str">
-        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M41" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N41" t="str">
         <v>Sí</v>
@@ -2215,22 +2215,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C42" t="str">
-        <v>JAVIER GARCIA ROSELLO</v>
+        <v>ALEXIS GARCIA VALERO</v>
       </c>
       <c r="D42">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="E42" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F42" t="str">
-        <v>00:00:43.21</v>
+        <v>00:00:39.46</v>
       </c>
       <c r="G42">
-        <v>137</v>
+        <v>180</v>
       </c>
       <c r="H42" s="1">
-        <v>44709.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I42" t="str">
         <v>Deportista</v>
@@ -2239,16 +2239,16 @@
         <v>50m</v>
       </c>
       <c r="K42" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L42" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M42" t="str">
-        <v>Sedavi</v>
+        <v>Elche</v>
       </c>
       <c r="N42" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="43">
@@ -2259,22 +2259,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C43" t="str">
-        <v>ADRIAN GARCIA GAZQUEZ</v>
+        <v>IKER BARTOLIN GIMENEZ</v>
       </c>
       <c r="D43">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="E43" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F43" t="str">
-        <v>00:00:43.54</v>
+        <v>00:00:43.21</v>
       </c>
       <c r="G43">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H43" s="1">
-        <v>42385.99949074074</v>
+        <v>45255.99949074074</v>
       </c>
       <c r="I43" t="str">
         <v>Deportista</v>
@@ -2283,16 +2283,16 @@
         <v>50m</v>
       </c>
       <c r="K43" t="str">
-        <v>Manual</v>
-      </c>
-      <c r="L43">
-        <v>201611612001</v>
+        <v>Electrónico</v>
+      </c>
+      <c r="L43" t="str">
+        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
       </c>
       <c r="M43" t="str">
-        <v>CASTELLON</v>
+        <v>Castellón</v>
       </c>
       <c r="N43" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="44">
@@ -2303,22 +2303,22 @@
         <v>50 Mariposa</v>
       </c>
       <c r="C44" t="str">
-        <v>VICENTE SILLA TAMARIT</v>
+        <v>JAVIER GARCIA ROSELLO</v>
       </c>
       <c r="D44">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="E44" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F44" t="str">
-        <v>00:00:43.96</v>
+        <v>00:00:43.21</v>
       </c>
       <c r="G44">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="H44" s="1">
-        <v>45683.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I44" t="str">
         <v>Deportista</v>
@@ -2327,42 +2327,42 @@
         <v>50m</v>
       </c>
       <c r="K44" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L44" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M44" t="str">
-        <v>Elche</v>
+        <v>Sedavi</v>
       </c>
       <c r="N44" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>100 Mariposa</v>
+        <v>50 Mariposa</v>
       </c>
       <c r="C45" t="str">
-        <v>TYMOFII VLASENKO</v>
+        <v>ADRIAN GARCIA GAZQUEZ</v>
       </c>
       <c r="D45">
-        <v>2007</v>
+        <v>2000</v>
       </c>
       <c r="E45" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F45" t="str">
-        <v>00:01:00.23</v>
+        <v>00:00:43.54</v>
       </c>
       <c r="G45">
-        <v>553</v>
+        <v>134</v>
       </c>
       <c r="H45" s="1">
-        <v>45094.99949074074</v>
+        <v>42385.99949074074</v>
       </c>
       <c r="I45" t="str">
         <v>Deportista</v>
@@ -2371,13 +2371,13 @@
         <v>50m</v>
       </c>
       <c r="K45" t="str">
-        <v>Electrónico</v>
-      </c>
-      <c r="L45" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>Manual</v>
+      </c>
+      <c r="L45">
+        <v>201611612001</v>
       </c>
       <c r="M45" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N45" t="str">
         <v>No</v>
@@ -2385,28 +2385,28 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>100 Mariposa</v>
+        <v>50 Mariposa</v>
       </c>
       <c r="C46" t="str">
-        <v>DAVID MUÑOZ CEBOLLA</v>
+        <v>VICENTE SILLA TAMARIT</v>
       </c>
       <c r="D46">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="E46" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F46" t="str">
-        <v>00:01:03.39</v>
+        <v>00:00:43.96</v>
       </c>
       <c r="G46">
-        <v>475</v>
+        <v>130</v>
       </c>
       <c r="H46" s="1">
-        <v>46075.99949074074</v>
+        <v>45683.99949074074</v>
       </c>
       <c r="I46" t="str">
         <v>Deportista</v>
@@ -2418,39 +2418,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L46" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M46" t="str">
         <v>Elche</v>
       </c>
       <c r="N46" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B47" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C47" t="str">
-        <v>ENRIQUE GALLIFA TRONCH</v>
+        <v>TYMOFII VLASENKO</v>
       </c>
       <c r="D47">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="E47" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F47" t="str">
-        <v>00:01:03.45</v>
+        <v>00:01:00.23</v>
       </c>
       <c r="G47">
-        <v>473</v>
+        <v>553</v>
       </c>
       <c r="H47" s="1">
-        <v>45682.99949074074</v>
+        <v>45094.99949074074</v>
       </c>
       <c r="I47" t="str">
         <v>Deportista</v>
@@ -2462,10 +2462,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L47" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M47" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N47" t="str">
         <v>No</v>
@@ -2473,28 +2473,28 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B48" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C48" t="str">
-        <v>NEIZAN DE LUCA RUBIO</v>
+        <v>DAVID MUÑOZ CEBOLLA</v>
       </c>
       <c r="D48">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="E48" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F48" t="str">
-        <v>00:01:05.81</v>
+        <v>00:01:03.39</v>
       </c>
       <c r="G48">
-        <v>424</v>
+        <v>475</v>
       </c>
       <c r="H48" s="1">
-        <v>46082.99949074074</v>
+        <v>46075.99949074074</v>
       </c>
       <c r="I48" t="str">
         <v>Deportista</v>
@@ -2506,10 +2506,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L48" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
       </c>
       <c r="M48" t="str">
-        <v>CASTELLÓN</v>
+        <v>Elche</v>
       </c>
       <c r="N48" t="str">
         <v>No</v>
@@ -2517,28 +2517,28 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B49" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C49" t="str">
-        <v>GERMAN RUIZ FITA</v>
+        <v>ENRIQUE GALLIFA TRONCH</v>
       </c>
       <c r="D49">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="E49" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F49" t="str">
-        <v>00:01:06.59</v>
+        <v>00:01:03.45</v>
       </c>
       <c r="G49">
-        <v>410</v>
+        <v>473</v>
       </c>
       <c r="H49" s="1">
-        <v>46075.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I49" t="str">
         <v>Deportista</v>
@@ -2550,7 +2550,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L49" t="str">
-        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M49" t="str">
         <v>Elche</v>
@@ -2561,28 +2561,28 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B50" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C50" t="str">
-        <v>JORDI SOLERA PAREDES</v>
+        <v>NEIZAN DE LUCA RUBIO</v>
       </c>
       <c r="D50">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="E50" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F50" t="str">
-        <v>00:01:07.04</v>
+        <v>00:01:05.81</v>
       </c>
       <c r="G50">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="H50" s="1">
-        <v>46173.99949074074</v>
+        <v>46082.99949074074</v>
       </c>
       <c r="I50" t="str">
         <v>Deportista</v>
@@ -2591,42 +2591,42 @@
         <v>50m</v>
       </c>
       <c r="K50" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L50" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M50" t="str">
-        <v>Vila-Real</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N50" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B51" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C51" t="str">
-        <v>MARCOS ESCOBEDO IRURETA</v>
+        <v>GERMAN RUIZ FITA</v>
       </c>
       <c r="D51">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="E51" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F51" t="str">
-        <v>00:01:08.72</v>
+        <v>00:01:06.59</v>
       </c>
       <c r="G51">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="H51" s="1">
-        <v>45682.99949074074</v>
+        <v>46075.99949074074</v>
       </c>
       <c r="I51" t="str">
         <v>Deportista</v>
@@ -2638,7 +2638,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L51" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>CAMPEONATO AUTONOMICO JUNIOR Y ABSOLUTO DE INVIERNO 2026</v>
       </c>
       <c r="M51" t="str">
         <v>Elche</v>
@@ -2649,28 +2649,28 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B52" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C52" t="str">
-        <v>CARLOS MENDEZ SALVADOR</v>
+        <v>JORDI SOLERA PAREDES</v>
       </c>
       <c r="D52">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="E52" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F52" t="str">
-        <v>00:01:09.02</v>
+        <v>00:01:07.04</v>
       </c>
       <c r="G52">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="H52" s="1">
-        <v>46145.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I52" t="str">
         <v>Deportista</v>
@@ -2679,13 +2679,13 @@
         <v>50m</v>
       </c>
       <c r="K52" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L52" t="str">
-        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M52" t="str">
-        <v>ZARAGOZA (C)</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N52" t="str">
         <v>Sí</v>
@@ -2693,28 +2693,28 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B53" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C53" t="str">
-        <v>SANTIAGO VICENTE TORNERO</v>
+        <v>MARCOS ESCOBEDO IRURETA</v>
       </c>
       <c r="D53">
-        <v>1994</v>
+        <v>2008</v>
       </c>
       <c r="E53" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F53" t="str">
-        <v>00:01:10.97</v>
+        <v>00:01:08.72</v>
       </c>
       <c r="G53">
-        <v>338</v>
+        <v>373</v>
       </c>
       <c r="H53" s="1">
-        <v>43638.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I53" t="str">
         <v>Deportista</v>
@@ -2723,42 +2723,42 @@
         <v>50m</v>
       </c>
       <c r="K53" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L53" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M53" t="str">
-        <v>Moncada</v>
+        <v>Elche</v>
       </c>
       <c r="N53" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B54" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C54" t="str">
-        <v>ONOFRE BONDIA VELERT</v>
+        <v>CARLOS MENDEZ SALVADOR</v>
       </c>
       <c r="D54">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="E54" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F54" t="str">
-        <v>00:01:11.12</v>
+        <v>00:01:09.02</v>
       </c>
       <c r="G54">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="H54" s="1">
-        <v>44576.99949074074</v>
+        <v>46145.99949074074</v>
       </c>
       <c r="I54" t="str">
         <v>Deportista</v>
@@ -2770,39 +2770,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L54" t="str">
-        <v>Autonomico Infantil de Invierno</v>
+        <v>XX TROFEO INTERNACIONAL IBERCAJA CIUDAD ZARAGOZA 2026 XVII MEMORIAL EDUARDO LASTRADA</v>
       </c>
       <c r="M54" t="str">
-        <v>Elche</v>
+        <v>ZARAGOZA (C)</v>
       </c>
       <c r="N54" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B55" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C55" t="str">
-        <v>MATEO ROJAS SUAY</v>
+        <v>SANTIAGO VICENTE TORNERO</v>
       </c>
       <c r="D55">
-        <v>2007</v>
+        <v>1994</v>
       </c>
       <c r="E55" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F55" t="str">
-        <v>00:01:12.14</v>
+        <v>00:01:10.97</v>
       </c>
       <c r="G55">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="H55" s="1">
-        <v>45094.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I55" t="str">
         <v>Deportista</v>
@@ -2811,42 +2811,42 @@
         <v>50m</v>
       </c>
       <c r="K55" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L55" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M55" t="str">
-        <v>Castellón</v>
+        <v>Moncada</v>
       </c>
       <c r="N55" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B56" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C56" t="str">
-        <v>MIGUEL BAIXAULI MUÑOZ</v>
+        <v>ONOFRE BONDIA VELERT</v>
       </c>
       <c r="D56">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="E56" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F56" t="str">
-        <v>00:01:12.22</v>
+        <v>00:01:11.12</v>
       </c>
       <c r="G56">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="H56" s="1">
-        <v>43631.99949074074</v>
+        <v>44576.99949074074</v>
       </c>
       <c r="I56" t="str">
         <v>Deportista</v>
@@ -2858,10 +2858,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L56" t="str">
-        <v>VIII Trofeo Real Club Natación Delfín-Control Calendario Único</v>
+        <v>Autonomico Infantil de Invierno</v>
       </c>
       <c r="M56" t="str">
-        <v>Valencia</v>
+        <v>Elche</v>
       </c>
       <c r="N56" t="str">
         <v>No</v>
@@ -2869,28 +2869,28 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B57" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C57" t="str">
-        <v>GONZALO YUSTE TRUJILLO</v>
+        <v>MATEO ROJAS SUAY</v>
       </c>
       <c r="D57">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E57" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F57" t="str">
-        <v>00:01:12.43</v>
+        <v>00:01:12.14</v>
       </c>
       <c r="G57">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H57" s="1">
-        <v>46046.99949074074</v>
+        <v>45094.99949074074</v>
       </c>
       <c r="I57" t="str">
         <v>Deportista</v>
@@ -2902,10 +2902,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L57" t="str">
-        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M57" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N57" t="str">
         <v>No</v>
@@ -2913,28 +2913,28 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B58" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C58" t="str">
-        <v>GEORGI ZHELYAZKOV</v>
+        <v>MIGUEL BAIXAULI MUÑOZ</v>
       </c>
       <c r="D58">
-        <v>2010</v>
+        <v>2001</v>
       </c>
       <c r="E58" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F58" t="str">
-        <v>00:01:12.81</v>
+        <v>00:01:12.22</v>
       </c>
       <c r="G58">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="H58" s="1">
-        <v>46172.99949074074</v>
+        <v>43631.99949074074</v>
       </c>
       <c r="I58" t="str">
         <v>Deportista</v>
@@ -2943,13 +2943,13 @@
         <v>50m</v>
       </c>
       <c r="K58" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L58" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>VIII Trofeo Real Club Natación Delfín-Control Calendario Único</v>
       </c>
       <c r="M58" t="str">
-        <v>Vila-Real</v>
+        <v>Valencia</v>
       </c>
       <c r="N58" t="str">
         <v>No</v>
@@ -2957,28 +2957,28 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B59" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C59" t="str">
-        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
+        <v>GONZALO YUSTE TRUJILLO</v>
       </c>
       <c r="D59">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="E59" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F59" t="str">
-        <v>00:01:13.56</v>
+        <v>00:01:12.43</v>
       </c>
       <c r="G59">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="H59" s="1">
-        <v>43267.99949074074</v>
+        <v>46046.99949074074</v>
       </c>
       <c r="I59" t="str">
         <v>Deportista</v>
@@ -2990,10 +2990,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L59" t="str">
-        <v>VII TROFEO REAL CLUB NATACION DELFIN</v>
+        <v>TROFEO INTERNACIONAL XXXI MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M59" t="str">
-        <v>PARQUE OESTE</v>
+        <v>Elche</v>
       </c>
       <c r="N59" t="str">
         <v>No</v>
@@ -3001,28 +3001,28 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B60" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C60" t="str">
-        <v>DANIEL FERNANDEZ CARO</v>
+        <v>GEORGI ZHELYAZKOV</v>
       </c>
       <c r="D60">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="E60" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F60" t="str">
-        <v>00:01:15.23</v>
+        <v>00:01:12.81</v>
       </c>
       <c r="G60">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="H60" s="1">
-        <v>45409.99949074074</v>
+        <v>46172.99949074074</v>
       </c>
       <c r="I60" t="str">
         <v>Deportista</v>
@@ -3031,13 +3031,13 @@
         <v>50m</v>
       </c>
       <c r="K60" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L60" t="str">
-        <v>TROFEO INTERNACIONAL XXVIX MEMORIAL PASCUAL ROMÁN</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M60" t="str">
-        <v>Elche</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N60" t="str">
         <v>No</v>
@@ -3045,28 +3045,28 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B61" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C61" t="str">
-        <v>RAUL PEREZ PEIRATS</v>
+        <v>MARC FERRANDIS-GARCIA CLEMENT</v>
       </c>
       <c r="D61">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="E61" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F61" t="str">
-        <v>00:01:15.94</v>
+        <v>00:01:13.56</v>
       </c>
       <c r="G61">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="H61" s="1">
-        <v>44359.99949074074</v>
+        <v>43267.99949074074</v>
       </c>
       <c r="I61" t="str">
         <v>Deportista</v>
@@ -3078,10 +3078,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L61" t="str">
-        <v>IX Trofeo Real Club Natación Delfín</v>
+        <v>VII TROFEO REAL CLUB NATACION DELFIN</v>
       </c>
       <c r="M61" t="str">
-        <v>Sedavi</v>
+        <v>PARQUE OESTE</v>
       </c>
       <c r="N61" t="str">
         <v>No</v>
@@ -3089,28 +3089,28 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B62" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C62" t="str">
-        <v>FLAVIUS MUSCALU</v>
+        <v>DANIEL FERNANDEZ CARO</v>
       </c>
       <c r="D62">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="E62" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F62" t="str">
-        <v>00:01:16.41</v>
+        <v>00:01:15.23</v>
       </c>
       <c r="G62">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="H62" s="1">
-        <v>44975.99949074074</v>
+        <v>45409.99949074074</v>
       </c>
       <c r="I62" t="str">
         <v>Deportista</v>
@@ -3122,7 +3122,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L62" t="str">
-        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
+        <v>TROFEO INTERNACIONAL XXVIX MEMORIAL PASCUAL ROMÁN</v>
       </c>
       <c r="M62" t="str">
         <v>Elche</v>
@@ -3133,28 +3133,28 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B63" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C63" t="str">
-        <v>DAVID HERREROS COLL</v>
+        <v>RAUL PEREZ PEIRATS</v>
       </c>
       <c r="D63">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="E63" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F63" t="str">
-        <v>00:01:16.77</v>
+        <v>00:01:15.94</v>
       </c>
       <c r="G63">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="H63" s="1">
-        <v>44612.99949074074</v>
+        <v>44359.99949074074</v>
       </c>
       <c r="I63" t="str">
         <v>Deportista</v>
@@ -3163,13 +3163,13 @@
         <v>50m</v>
       </c>
       <c r="K63" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L63" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>IX Trofeo Real Club Natación Delfín</v>
       </c>
       <c r="M63" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N63" t="str">
         <v>No</v>
@@ -3177,28 +3177,28 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B64" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C64" t="str">
-        <v>JUAN CAMACHO MARTINEZ</v>
+        <v>FLAVIUS MUSCALU</v>
       </c>
       <c r="D64">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="E64" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F64" t="str">
-        <v>00:01:17.12</v>
+        <v>00:01:16.41</v>
       </c>
       <c r="G64">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="H64" s="1">
-        <v>45710.99949074074</v>
+        <v>44975.99949074074</v>
       </c>
       <c r="I64" t="str">
         <v>Deportista</v>
@@ -3210,24 +3210,24 @@
         <v>Electrónico</v>
       </c>
       <c r="L64" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
+        <v>Trofeo Internacional XXVIII Memorial Pascual Roman</v>
       </c>
       <c r="M64" t="str">
-        <v>ELCHE</v>
+        <v>Elche</v>
       </c>
       <c r="N64" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B65" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C65" t="str">
-        <v>MARTIN FABIA NOGUERA</v>
+        <v>DAVID HERREROS COLL</v>
       </c>
       <c r="D65">
         <v>2007</v>
@@ -3236,10 +3236,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F65" t="str">
-        <v>00:01:20.22</v>
+        <v>00:01:16.77</v>
       </c>
       <c r="G65">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="H65" s="1">
         <v>44612.99949074074</v>
@@ -3265,13 +3265,13 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B66" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C66" t="str">
-        <v>GEORGI ZHELYAZKOV</v>
+        <v>JUAN CAMACHO MARTINEZ</v>
       </c>
       <c r="D66">
         <v>2010</v>
@@ -3280,13 +3280,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F66" t="str">
-        <v>00:01:20.31</v>
+        <v>00:01:17.12</v>
       </c>
       <c r="G66">
-        <v>233</v>
+        <v>264</v>
       </c>
       <c r="H66" s="1">
-        <v>45473.99949074074</v>
+        <v>45710.99949074074</v>
       </c>
       <c r="I66" t="str">
         <v>Deportista</v>
@@ -3298,39 +3298,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L66" t="str">
-        <v>Autonomico Infantil de Verano</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2025 C.V.</v>
       </c>
       <c r="M66" t="str">
-        <v>Sedavi(Valencia)</v>
+        <v>ELCHE</v>
       </c>
       <c r="N66" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B67" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C67" t="str">
-        <v>HECTOR MARTINEZ GARCIA</v>
+        <v>MARTIN FABIA NOGUERA</v>
       </c>
       <c r="D67">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E67" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F67" t="str">
-        <v>00:01:23.71</v>
+        <v>00:01:20.22</v>
       </c>
       <c r="G67">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="H67" s="1">
-        <v>45682.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I67" t="str">
         <v>Deportista</v>
@@ -3339,27 +3339,27 @@
         <v>50m</v>
       </c>
       <c r="K67" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L67" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M67" t="str">
-        <v>Elche</v>
+        <v>Castellón</v>
       </c>
       <c r="N67" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B68" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C68" t="str">
-        <v>FEDERICO MANUEL HERMIDA BATTISTON</v>
+        <v>GEORGI ZHELYAZKOV</v>
       </c>
       <c r="D68">
         <v>2010</v>
@@ -3368,13 +3368,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F68" t="str">
-        <v>00:01:28.21</v>
+        <v>00:01:20.31</v>
       </c>
       <c r="G68">
-        <v>176</v>
+        <v>233</v>
       </c>
       <c r="H68" s="1">
-        <v>45682.99949074074</v>
+        <v>45473.99949074074</v>
       </c>
       <c r="I68" t="str">
         <v>Deportista</v>
@@ -3386,10 +3386,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L68" t="str">
-        <v>XXX MEMORIAL PASCUAL ROMAN</v>
+        <v>Autonomico Infantil de Verano</v>
       </c>
       <c r="M68" t="str">
-        <v>Elche</v>
+        <v>Sedavi(Valencia)</v>
       </c>
       <c r="N68" t="str">
         <v>No</v>
@@ -3397,28 +3397,28 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B69" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C69" t="str">
-        <v>VICTOR ROSELLO VALERA</v>
+        <v>HECTOR MARTINEZ GARCIA</v>
       </c>
       <c r="D69">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="E69" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F69" t="str">
-        <v>00:01:33.74</v>
+        <v>00:01:23.71</v>
       </c>
       <c r="G69">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="H69" s="1">
-        <v>44612.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I69" t="str">
         <v>Deportista</v>
@@ -3427,27 +3427,27 @@
         <v>50m</v>
       </c>
       <c r="K69" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L69" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M69" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N69" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B70" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C70" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>FEDERICO MANUEL HERMIDA BATTISTON</v>
       </c>
       <c r="D70">
         <v>2010</v>
@@ -3456,13 +3456,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F70" t="str">
-        <v>00:01:37.32</v>
+        <v>00:01:28.21</v>
       </c>
       <c r="G70">
-        <v>131</v>
+        <v>176</v>
       </c>
       <c r="H70" s="1">
-        <v>45255.99949074074</v>
+        <v>45682.99949074074</v>
       </c>
       <c r="I70" t="str">
         <v>Deportista</v>
@@ -3474,39 +3474,39 @@
         <v>Electrónico</v>
       </c>
       <c r="L70" t="str">
-        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
+        <v>XXX MEMORIAL PASCUAL ROMAN</v>
       </c>
       <c r="M70" t="str">
-        <v>Castellón</v>
+        <v>Elche</v>
       </c>
       <c r="N70" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B71" t="str">
         <v>100 Mariposa</v>
       </c>
       <c r="C71" t="str">
-        <v>RAFAEL ALBA TIRADO</v>
+        <v>VICTOR ROSELLO VALERA</v>
       </c>
       <c r="D71">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E71" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F71" t="str">
-        <v>00:01:47.48</v>
+        <v>00:01:33.74</v>
       </c>
       <c r="G71">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="H71" s="1">
-        <v>44611.99949074074</v>
+        <v>44612.99949074074</v>
       </c>
       <c r="I71" t="str">
         <v>Deportista</v>
@@ -3524,33 +3524,33 @@
         <v>Castellón</v>
       </c>
       <c r="N71" t="str">
-        <v>Sí</v>
+        <v>No</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B72" t="str">
-        <v>200 Mariposa</v>
+        <v>100 Mariposa</v>
       </c>
       <c r="C72" t="str">
-        <v>SANTIAGO VICENTE TORNERO</v>
+        <v>IKER BARTOLIN GIMENEZ</v>
       </c>
       <c r="D72">
-        <v>1994</v>
+        <v>2010</v>
       </c>
       <c r="E72" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F72" t="str">
-        <v>00:02:30.46</v>
+        <v>00:01:37.32</v>
       </c>
       <c r="G72">
-        <v>394</v>
+        <v>131</v>
       </c>
       <c r="H72" s="1">
-        <v>43638.99949074074</v>
+        <v>45255.99949074074</v>
       </c>
       <c r="I72" t="str">
         <v>Deportista</v>
@@ -3559,42 +3559,42 @@
         <v>50m</v>
       </c>
       <c r="K72" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L72" t="str">
-        <v>7ª Jornada Control infa y mayores</v>
+        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
       </c>
       <c r="M72" t="str">
-        <v>Moncada</v>
+        <v>Castellón</v>
       </c>
       <c r="N72" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B73" t="str">
-        <v>200 Mariposa</v>
+        <v>100 Mariposa</v>
       </c>
       <c r="C73" t="str">
-        <v>DAVID MUÑOZ CEBOLLA</v>
+        <v>RAFAEL ALBA TIRADO</v>
       </c>
       <c r="D73">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="E73" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F73" t="str">
-        <v>00:02:33.62</v>
+        <v>00:01:47.48</v>
       </c>
       <c r="G73">
-        <v>371</v>
+        <v>97</v>
       </c>
       <c r="H73" s="1">
-        <v>45472.99949074074</v>
+        <v>44611.99949074074</v>
       </c>
       <c r="I73" t="str">
         <v>Deportista</v>
@@ -3603,42 +3603,42 @@
         <v>50m</v>
       </c>
       <c r="K73" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L73" t="str">
-        <v>Autonomico Infantil de Verano</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M73" t="str">
-        <v>Sedavi(Valencia)</v>
+        <v>Castellón</v>
       </c>
       <c r="N73" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B74" t="str">
         <v>200 Mariposa</v>
       </c>
       <c r="C74" t="str">
-        <v>MARCOS ESCOBEDO IRURETA</v>
+        <v>SANTIAGO VICENTE TORNERO</v>
       </c>
       <c r="D74">
-        <v>2008</v>
+        <v>1994</v>
       </c>
       <c r="E74" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F74" t="str">
-        <v>00:02:35.30</v>
+        <v>00:02:30.46</v>
       </c>
       <c r="G74">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="H74" s="1">
-        <v>45095.99949074074</v>
+        <v>43638.99949074074</v>
       </c>
       <c r="I74" t="str">
         <v>Deportista</v>
@@ -3647,13 +3647,13 @@
         <v>50m</v>
       </c>
       <c r="K74" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L74" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>7ª Jornada Control infa y mayores</v>
       </c>
       <c r="M74" t="str">
-        <v>Castellón</v>
+        <v>Moncada</v>
       </c>
       <c r="N74" t="str">
         <v>No</v>
@@ -3661,28 +3661,28 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B75" t="str">
         <v>200 Mariposa</v>
       </c>
       <c r="C75" t="str">
-        <v>JORDI SOLERA PAREDES</v>
+        <v>DAVID MUÑOZ CEBOLLA</v>
       </c>
       <c r="D75">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E75" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F75" t="str">
-        <v>00:02:36.72</v>
+        <v>00:02:33.62</v>
       </c>
       <c r="G75">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="H75" s="1">
-        <v>46173.99949074074</v>
+        <v>45472.99949074074</v>
       </c>
       <c r="I75" t="str">
         <v>Deportista</v>
@@ -3691,13 +3691,13 @@
         <v>50m</v>
       </c>
       <c r="K75" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L75" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>Autonomico Infantil de Verano</v>
       </c>
       <c r="M75" t="str">
-        <v>Vila-Real</v>
+        <v>Sedavi(Valencia)</v>
       </c>
       <c r="N75" t="str">
         <v>No</v>
@@ -3705,28 +3705,28 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B76" t="str">
         <v>200 Mariposa</v>
       </c>
       <c r="C76" t="str">
-        <v>MATEO ROJAS SUAY</v>
+        <v>MARCOS ESCOBEDO IRURETA</v>
       </c>
       <c r="D76">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="E76" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F76" t="str">
-        <v>00:02:40.60</v>
+        <v>00:02:35.30</v>
       </c>
       <c r="G76">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="H76" s="1">
-        <v>45255.99949074074</v>
+        <v>45095.99949074074</v>
       </c>
       <c r="I76" t="str">
         <v>Deportista</v>
@@ -3738,7 +3738,7 @@
         <v>Electrónico</v>
       </c>
       <c r="L76" t="str">
-        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M76" t="str">
         <v>Castellón</v>
@@ -3749,25 +3749,25 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B77" t="str">
         <v>200 Mariposa</v>
       </c>
       <c r="C77" t="str">
-        <v>GEORGI ZHELYAZKOV</v>
+        <v>JORDI SOLERA PAREDES</v>
       </c>
       <c r="D77">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="E77" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F77" t="str">
-        <v>00:02:49.80</v>
+        <v>00:02:36.72</v>
       </c>
       <c r="G77">
-        <v>274</v>
+        <v>349</v>
       </c>
       <c r="H77" s="1">
         <v>46173.99949074074</v>
@@ -3793,13 +3793,13 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B78" t="str">
         <v>200 Mariposa</v>
       </c>
       <c r="C78" t="str">
-        <v>DAVID HERREROS COLL</v>
+        <v>MATEO ROJAS SUAY</v>
       </c>
       <c r="D78">
         <v>2007</v>
@@ -3808,13 +3808,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F78" t="str">
-        <v>00:03:04.01</v>
+        <v>00:02:40.60</v>
       </c>
       <c r="G78">
-        <v>216</v>
+        <v>324</v>
       </c>
       <c r="H78" s="1">
-        <v>44611.99949074074</v>
+        <v>45255.99949074074</v>
       </c>
       <c r="I78" t="str">
         <v>Deportista</v>
@@ -3823,10 +3823,10 @@
         <v>50m</v>
       </c>
       <c r="K78" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L78" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
       </c>
       <c r="M78" t="str">
         <v>Castellón</v>
@@ -3837,28 +3837,28 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B79" t="str">
         <v>200 Mariposa</v>
       </c>
       <c r="C79" t="str">
-        <v>MARTIN FABIA NOGUERA</v>
+        <v>GEORGI ZHELYAZKOV</v>
       </c>
       <c r="D79">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="E79" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F79" t="str">
-        <v>00:03:08.60</v>
+        <v>00:02:49.80</v>
       </c>
       <c r="G79">
-        <v>200</v>
+        <v>274</v>
       </c>
       <c r="H79" s="1">
-        <v>44611.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I79" t="str">
         <v>Deportista</v>
@@ -3870,10 +3870,10 @@
         <v>Manual</v>
       </c>
       <c r="L79" t="str">
-        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M79" t="str">
-        <v>Castellón</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N79" t="str">
         <v>No</v>
@@ -3881,28 +3881,28 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B80" t="str">
         <v>200 Mariposa</v>
       </c>
       <c r="C80" t="str">
-        <v>IKER BARTOLIN GIMENEZ</v>
+        <v>DAVID HERREROS COLL</v>
       </c>
       <c r="D80">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E80" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F80" t="str">
-        <v>00:03:26.78</v>
+        <v>00:03:04.01</v>
       </c>
       <c r="G80">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="H80" s="1">
-        <v>45255.99949074074</v>
+        <v>44611.99949074074</v>
       </c>
       <c r="I80" t="str">
         <v>Deportista</v>
@@ -3911,10 +3911,10 @@
         <v>50m</v>
       </c>
       <c r="K80" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L80" t="str">
-        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
       </c>
       <c r="M80" t="str">
         <v>Castellón</v>
@@ -3925,13 +3925,13 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B81" t="str">
         <v>200 Mariposa</v>
       </c>
       <c r="C81" t="str">
-        <v>RAFAEL ALBA TIRADO</v>
+        <v>MARTIN FABIA NOGUERA</v>
       </c>
       <c r="D81">
         <v>2007</v>
@@ -3940,10 +3940,10 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F81" t="str">
-        <v>00:03:41.92</v>
+        <v>00:03:08.60</v>
       </c>
       <c r="G81">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="H81" s="1">
         <v>44611.99949074074</v>
@@ -3967,9 +3967,97 @@
         <v>No</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82">
+        <v>9</v>
+      </c>
+      <c r="B82" t="str">
+        <v>200 Mariposa</v>
+      </c>
+      <c r="C82" t="str">
+        <v>IKER BARTOLIN GIMENEZ</v>
+      </c>
+      <c r="D82">
+        <v>2010</v>
+      </c>
+      <c r="E82" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F82" t="str">
+        <v>00:03:26.78</v>
+      </c>
+      <c r="G82">
+        <v>152</v>
+      </c>
+      <c r="H82" s="1">
+        <v>45255.99949074074</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J82" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Electrónico</v>
+      </c>
+      <c r="L82" t="str">
+        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
+      </c>
+      <c r="M82" t="str">
+        <v>Castellón</v>
+      </c>
+      <c r="N82" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>10</v>
+      </c>
+      <c r="B83" t="str">
+        <v>200 Mariposa</v>
+      </c>
+      <c r="C83" t="str">
+        <v>RAFAEL ALBA TIRADO</v>
+      </c>
+      <c r="D83">
+        <v>2007</v>
+      </c>
+      <c r="E83" t="str">
+        <v>C.N. MEDITERRANEO VALENCIA</v>
+      </c>
+      <c r="F83" t="str">
+        <v>00:03:41.92</v>
+      </c>
+      <c r="G83">
+        <v>123</v>
+      </c>
+      <c r="H83" s="1">
+        <v>44611.99949074074</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Deportista</v>
+      </c>
+      <c r="J83" t="str">
+        <v>50m</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="L83" t="str">
+        <v>4º Control Infantil Junior y Absoluto Castellón</v>
+      </c>
+      <c r="M83" t="str">
+        <v>Castellón</v>
+      </c>
+      <c r="N83" t="str">
+        <v>No</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O83"/>
   </ignoredErrors>
 </worksheet>
 </file>